--- a/data/merged/2026-09-09/MERGED_ES_Wet-Dry-Floor-Washer_2026-09-09.xlsx
+++ b/data/merged/2026-09-09/MERGED_ES_Wet-Dry-Floor-Washer_2026-09-09.xlsx
@@ -1174,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR8"/>
+  <dimension ref="A1:BR7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -2241,40 +2241,40 @@
       <c r="B5" s="13"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>B0D2KT41N3</t>
+          <t>B0H2D3H8RR</t>
         </is>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>Ultenic</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0D2KT41N3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/Ultenic/page/0909B0E2-6E16-41A6-9F7F-96DB127DBF91?lp_asin=B0H2D3H8RR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Aspiradora con Cable en Seco y Húmedos - Aspirador Sólidos y Líquidos 16L Conga Rockstar Wet &amp; Dry Compact Garden Plu</t>
+          <t>Ultenic Fregona EléctricasAspirador Lava y Friega 3 en 1 | Autolimpieza y 180° Plegable | Limpieza de Bordes 0 mm | hasta 5</t>
         </is>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0D2KT41N3?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H2D3H8RR?psc=1</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71zwr1xxvzL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31WDLyP9wrL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>B0D2KT41N3</t>
+          <t>B0H2D3H8RR</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
@@ -2288,13 +2288,11 @@
         </is>
       </c>
       <c r="O5" s="15">
-        <v>2233</v>
-      </c>
-      <c r="P5" s="15">
-        <v>-552</v>
-      </c>
+        <v>97198</v>
+      </c>
+      <c r="P5" s="15"/>
       <c r="Q5" s="16">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
@@ -2303,61 +2301,53 @@
       </c>
       <c r="S5" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T5" s="15">
-        <v>466</v>
-      </c>
-      <c r="U5" s="16">
-        <v>1.28</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="U5" s="16"/>
       <c r="V5" s="15">
-        <v>18593</v>
-      </c>
-      <c r="W5" s="15" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="X5" s="15">
-        <v>11970</v>
-      </c>
+        <v>912</v>
+      </c>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
       <c r="Y5" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z5" s="20">
-        <v>32.98</v>
+        <v>188.42</v>
       </c>
       <c r="AA5"/>
       <c r="AB5"/>
       <c r="AC5" s="2"/>
       <c r="AD5" s="19">
-        <v>922</v>
+        <v>13</v>
       </c>
       <c r="AE5" s="15">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AF5" s="21">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AG5" s="22">
-        <v>0.0858</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="20">
-        <v>10.1</v>
+        <v>11.58</v>
       </c>
       <c r="AI5" s="16">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AJ5"/>
       <c r="AK5" s="13" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AL5" s="19">
-        <v>866</v>
+        <v>56</v>
       </c>
       <c r="AM5" s="13" t="inlineStr">
         <is>
@@ -2371,7 +2361,7 @@
         <v>10</v>
       </c>
       <c r="AR5" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS5" s="14" t="inlineStr">
         <is>
@@ -2386,11 +2376,7 @@
       <c r="AU5" s="13"/>
       <c r="AV5" s="14"/>
       <c r="AW5" s="13"/>
-      <c r="AX5" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AX5" s="13"/>
       <c r="AY5" s="13"/>
       <c r="AZ5" s="13"/>
       <c r="BA5" s="13"/>
@@ -2412,42 +2398,38 @@
       <c r="BI5"/>
       <c r="BJ5" s="23" t="inlineStr">
         <is>
-          <t>4.5 kg</t>
+          <t>8,05 Libras</t>
         </is>
       </c>
       <c r="BK5" s="23" t="inlineStr">
         <is>
-          <t>4.50 kg</t>
+          <t>3.65 kg</t>
         </is>
       </c>
       <c r="BL5" s="23" t="inlineStr">
         <is>
-          <t>38 x 33 x 45 cm</t>
-        </is>
-      </c>
-      <c r="BM5" s="23" t="inlineStr">
-        <is>
-          <t>38.00 x 33.00 x 45.00 cm</t>
-        </is>
-      </c>
+          <t>22,6l. x 27an. x 114,7al. centímetros</t>
+        </is>
+      </c>
+      <c r="BM5" s="23"/>
       <c r="BN5" s="23" t="inlineStr">
         <is>
-          <t>5.37 kg</t>
+          <t>6.49 kg</t>
         </is>
       </c>
       <c r="BO5" s="23" t="inlineStr">
         <is>
-          <t>5.37 kg</t>
+          <t>6.49 kg</t>
         </is>
       </c>
       <c r="BP5" s="23" t="inlineStr">
         <is>
-          <t>40 x 36 x 36 cm</t>
+          <t>73.5 x 37.2 x 26 cm</t>
         </is>
       </c>
       <c r="BQ5" s="23" t="inlineStr">
         <is>
-          <t>40.00 x 36.00 x 36.00 cm</t>
+          <t>73.50 x 37.20 x 26.00 cm</t>
         </is>
       </c>
       <c r="BR5" s="13" t="inlineStr">
@@ -2463,40 +2445,48 @@
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>B0H2D3H8RR</t>
+          <t>B0H8ZM49W9</t>
         </is>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Ultenic</t>
+          <t>KSIWEHDSS</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Ultenic/page/0909B0E2-6E16-41A6-9F7F-96DB127DBF91?lp_asin=B0H2D3H8RR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=KSIWEHDSS</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Ultenic Fregona EléctricasAspirador Lava y Friega 3 en 1 | Autolimpieza y 180° Plegable | Limpieza de Bordes 0 mm | hasta 5</t>
-        </is>
-      </c>
-      <c r="I6" s="14"/>
+          <t>Aspiradoras de Mano, Aspirador Coche Potente 20000Pa,Recargable Aspiradora De Mano Sin Cable,Mini Aspiradora para Hogar,Pelo de Mascotas</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>【Potente succión de 20000Pa】Esta aspiradora de mano ofrece una potencia de 20000 Pa, perfecta para aspirar polvo, migas y líquidos derramados sin esfuerzo. Su motor de alto rendimiento garantiza una limpieza profunda en cualquier superficie, ya sea en seco o sobre pequeños derrames.
+【Ligera, portátil y fácil de guardar】Con un peso de solo 400 gramos, esta aspiradora de mano es tan compacta que no ocupa espacio y cabe en cualquier rincón del hogar o del coche. Su diseño ergonómico permite usarla cómodamente con una sola mano, ideal para llevarla de viaje o para limpiezas rápidas. Las aspiradoras de mano como esta hacen que la limpieza diaria sea muy cómoda.
+【Carga rápida】Esta aspiradora de mano se carga rápidamente y te ofrece entre 20 y 30 minutos de uso continuo. Es perfecta para limpiezas exprés sin interrupciones. Tener siempre lista una aspiradora de mano en pocos minutos es la solución más práctica para mantener tu espacio impecable en todo momento.
+【Filtro lavable y reutilizable】El filtro de esta aspiradora de mano es totalmente lavable con agua, lo que permite un mantenimiento sencillo y conserva la máxima potencia de succión durante más tiempo. Las aspiradoras de mano con filtro lavable son más económicas, ya que no necesitas comprar recambios constantemente y reduces residuos.
+【Funcionamiento silencioso por debajo de 73dB】A pesar de su gran potencia, esta aspiradora de mano funciona con un nivel de ruido inferior a 73 dB, mucho más silenciosa que otros modelos. Puedes limpiar sin molestar a tu familia ni a tus mascotas.</t>
+        </is>
+      </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0H2D3H8RR?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H8ZM49W9?psc=1</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31WDLyP9wrL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61BFtnogDAL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>B0H2D3H8RR</t>
+          <t>B0H8ZM49W9</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
@@ -2510,7 +2500,7 @@
         </is>
       </c>
       <c r="O6" s="15">
-        <v>97198</v>
+        <v>270047</v>
       </c>
       <c r="P6" s="15"/>
       <c r="Q6" s="16">
@@ -2523,7 +2513,7 @@
       </c>
       <c r="S6" s="18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T6" s="15">
@@ -2531,7 +2521,7 @@
       </c>
       <c r="U6" s="16"/>
       <c r="V6" s="15">
-        <v>912</v>
+        <v>144</v>
       </c>
       <c r="W6" s="15"/>
       <c r="X6" s="15"/>
@@ -2539,126 +2529,96 @@
         <v>1</v>
       </c>
       <c r="Z6" s="20">
-        <v>188.42</v>
+        <v>35.98</v>
       </c>
       <c r="AA6"/>
       <c r="AB6"/>
       <c r="AC6" s="2"/>
       <c r="AD6" s="19">
-        <v>13</v>
+        <v>11263</v>
       </c>
       <c r="AE6" s="15">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AF6" s="21">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AG6" s="22">
+        <v>0.75</v>
+      </c>
+      <c r="AH6" s="20"/>
+      <c r="AI6" s="16">
         <v>0</v>
-      </c>
-      <c r="AH6" s="20">
-        <v>11.58</v>
-      </c>
-      <c r="AI6" s="16">
-        <v>0.8</v>
       </c>
       <c r="AJ6"/>
       <c r="AK6" s="13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AL6" s="19">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="AM6" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN6" s="13"/>
       <c r="AO6" s="13"/>
       <c r="AP6"/>
       <c r="AQ6" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AR6" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS6" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>shanximeixiandingshengganggougongchengyouxiangon</t>
         </is>
       </c>
       <c r="AT6" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU6" s="13"/>
-      <c r="AV6" s="14"/>
-      <c r="AW6" s="13"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU6" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV6" s="14" t="inlineStr">
+        <is>
+          <t>宝鸡市 陕西 722300 CN</t>
+        </is>
+      </c>
+      <c r="AW6" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1IIXB8MBW34P6</t>
+        </is>
+      </c>
       <c r="AX6" s="13"/>
       <c r="AY6" s="13"/>
       <c r="AZ6" s="13"/>
       <c r="BA6" s="13"/>
       <c r="BB6" s="13"/>
-      <c r="BC6" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD6" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC6" s="13"/>
+      <c r="BD6" s="13"/>
       <c r="BE6" s="13"/>
       <c r="BF6" s="13"/>
       <c r="BG6" s="13"/>
       <c r="BH6" s="14"/>
       <c r="BI6"/>
-      <c r="BJ6" s="23" t="inlineStr">
-        <is>
-          <t>8,05 Libras</t>
-        </is>
-      </c>
-      <c r="BK6" s="23" t="inlineStr">
-        <is>
-          <t>3.65 kg</t>
-        </is>
-      </c>
-      <c r="BL6" s="23" t="inlineStr">
-        <is>
-          <t>22,6l. x 27an. x 114,7al. centímetros</t>
-        </is>
-      </c>
+      <c r="BJ6" s="23"/>
+      <c r="BK6" s="23"/>
+      <c r="BL6" s="23"/>
       <c r="BM6" s="23"/>
-      <c r="BN6" s="23" t="inlineStr">
-        <is>
-          <t>6.49 kg</t>
-        </is>
-      </c>
-      <c r="BO6" s="23" t="inlineStr">
-        <is>
-          <t>6.49 kg</t>
-        </is>
-      </c>
-      <c r="BP6" s="23" t="inlineStr">
-        <is>
-          <t>73.5 x 37.2 x 26 cm</t>
-        </is>
-      </c>
-      <c r="BQ6" s="23" t="inlineStr">
-        <is>
-          <t>73.50 x 37.20 x 26.00 cm</t>
-        </is>
-      </c>
-      <c r="BR6" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
+      <c r="BN6" s="23"/>
+      <c r="BO6" s="23"/>
+      <c r="BP6" s="23"/>
+      <c r="BQ6" s="23"/>
+      <c r="BR6" s="13"/>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
@@ -2667,48 +2627,40 @@
       <c r="B7" s="13"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>B0H8ZM49W9</t>
+          <t>B0DGV9F4X3</t>
         </is>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>KSIWEHDSS</t>
+          <t>Rowenta</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=KSIWEHDSS</t>
+          <t>https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>Aspiradoras de Mano, Aspirador Coche Potente 20000Pa,Recargable Aspiradora De Mano Sin Cable,Mini Aspiradora para Hogar,Pelo de Mascotas</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>【Potente succión de 20000Pa】Esta aspiradora de mano ofrece una potencia de 20000 Pa, perfecta para aspirar polvo, migas y líquidos derramados sin esfuerzo. Su motor de alto rendimiento garantiza una limpieza profunda en cualquier superficie, ya sea en seco o sobre pequeños derrames.
-【Ligera, portátil y fácil de guardar】Con un peso de solo 400 gramos, esta aspiradora de mano es tan compacta que no ocupa espacio y cabe en cualquier rincón del hogar o del coche. Su diseño ergonómico permite usarla cómodamente con una sola mano, ideal para llevarla de viaje o para limpiezas rápidas. Las aspiradoras de mano como esta hacen que la limpieza diaria sea muy cómoda.
-【Carga rápida】Esta aspiradora de mano se carga rápidamente y te ofrece entre 20 y 30 minutos de uso continuo. Es perfecta para limpiezas exprés sin interrupciones. Tener siempre lista una aspiradora de mano en pocos minutos es la solución más práctica para mantener tu espacio impecable en todo momento.
-【Filtro lavable y reutilizable】El filtro de esta aspiradora de mano es totalmente lavable con agua, lo que permite un mantenimiento sencillo y conserva la máxima potencia de succión durante más tiempo. Las aspiradoras de mano con filtro lavable son más económicas, ya que no necesitas comprar recambios constantemente y reduces residuos.
-【Funcionamiento silencioso por debajo de 73dB】A pesar de su gran potencia, esta aspiradora de mano funciona con un nivel de ruido inferior a 73 dB, mucho más silenciosa que otros modelos. Puedes limpiar sin molestar a tu familia ni a tus mascotas.</t>
-        </is>
-      </c>
+          <t>Rowenta X-Clean 4, Aspiradora Fregona Eléctrica Sin Cable, NegrosAspira y Friega a la vez, 200 W, Pantalla De Control Intel</t>
+        </is>
+      </c>
+      <c r="I7" s="14"/>
       <c r="J7" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0H8ZM49W9?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DGV9F4X3?psc=1</t>
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61BFtnogDAL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61ZOUuPZaJL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>B0H8ZM49W9</t>
+          <t>B0DGV9F4X3</t>
         </is>
       </c>
       <c r="M7" s="14" t="inlineStr">
@@ -2722,11 +2674,13 @@
         </is>
       </c>
       <c r="O7" s="15">
-        <v>270047</v>
-      </c>
-      <c r="P7" s="15"/>
+        <v>223844</v>
+      </c>
+      <c r="P7" s="15">
+        <v>-12404</v>
+      </c>
       <c r="Q7" s="16">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="R7" s="17" t="inlineStr">
         <is>
@@ -2735,314 +2689,138 @@
       </c>
       <c r="S7" s="18" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T7" s="15">
-        <v>4</v>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T7" s="15"/>
       <c r="U7" s="16"/>
-      <c r="V7" s="15">
-        <v>144</v>
-      </c>
+      <c r="V7" s="15"/>
       <c r="W7" s="15"/>
       <c r="X7" s="15"/>
       <c r="Y7" s="19">
         <v>1</v>
       </c>
       <c r="Z7" s="20">
-        <v>35.98</v>
+        <v>173.74</v>
       </c>
       <c r="AA7"/>
       <c r="AB7"/>
       <c r="AC7" s="2"/>
       <c r="AD7" s="19">
-        <v>11263</v>
+        <v>795</v>
       </c>
       <c r="AE7" s="15">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="AF7" s="21">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AG7" s="22">
-        <v>0.75</v>
-      </c>
-      <c r="AH7" s="20"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="20">
+        <v>11.58</v>
+      </c>
       <c r="AI7" s="16">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AJ7"/>
       <c r="AK7" s="13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AL7" s="19">
-        <v>15</v>
+        <v>670</v>
       </c>
       <c r="AM7" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN7" s="13"/>
       <c r="AO7" s="13"/>
       <c r="AP7"/>
       <c r="AQ7" s="19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AR7" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS7" s="14" t="inlineStr">
         <is>
-          <t>shanximeixiandingshengganggougongchengyouxiangon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT7" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU7" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV7" s="14" t="inlineStr">
-        <is>
-          <t>宝鸡市 陕西 722300 CN</t>
-        </is>
-      </c>
-      <c r="AW7" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1IIXB8MBW34P6</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU7" s="13"/>
+      <c r="AV7" s="14"/>
+      <c r="AW7" s="13"/>
       <c r="AX7" s="13"/>
       <c r="AY7" s="13"/>
       <c r="AZ7" s="13"/>
       <c r="BA7" s="13"/>
       <c r="BB7" s="13"/>
-      <c r="BC7" s="13"/>
-      <c r="BD7" s="13"/>
+      <c r="BC7" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD7" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE7" s="13"/>
       <c r="BF7" s="13"/>
       <c r="BG7" s="13"/>
       <c r="BH7" s="14"/>
       <c r="BI7"/>
-      <c r="BJ7" s="23"/>
-      <c r="BK7" s="23"/>
-      <c r="BL7" s="23"/>
-      <c r="BM7" s="23"/>
-      <c r="BN7" s="23"/>
-      <c r="BO7" s="23"/>
-      <c r="BP7" s="23"/>
-      <c r="BQ7" s="23"/>
-      <c r="BR7" s="13"/>
-    </row>
-    <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
-        <v>7</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>B0DGV9F4X3</t>
-        </is>
-      </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>Rowenta</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>Rowenta X-Clean 4, Aspiradora Fregona Eléctrica Sin Cable, NegrosAspira y Friega a la vez, 200 W, Pantalla De Control Intel</t>
-        </is>
-      </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0DGV9F4X3?psc=1</t>
-        </is>
-      </c>
-      <c r="K8" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61ZOUuPZaJL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>B0DGV9F4X3</t>
-        </is>
-      </c>
-      <c r="M8" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras domésticas para sólidos y líquidos</t>
-        </is>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O8" s="15">
-        <v>223844</v>
-      </c>
-      <c r="P8" s="15">
-        <v>-12404</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>-0.06</v>
-      </c>
-      <c r="R8" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras domésticas para sólidos y líquidos</t>
-        </is>
-      </c>
-      <c r="S8" s="18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T8" s="15"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="20">
-        <v>173.74</v>
-      </c>
-      <c r="AA8"/>
-      <c r="AB8"/>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="19">
-        <v>795</v>
-      </c>
-      <c r="AE8" s="15">
-        <v>35</v>
-      </c>
-      <c r="AF8" s="21">
-        <v>4.2</v>
-      </c>
-      <c r="AG8" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="20">
-        <v>11.58</v>
-      </c>
-      <c r="AI8" s="16">
-        <v>0.78</v>
-      </c>
-      <c r="AJ8"/>
-      <c r="AK8" s="13" t="inlineStr">
-        <is>
-          <t>2024-11-07</t>
-        </is>
-      </c>
-      <c r="AL8" s="19">
-        <v>670</v>
-      </c>
-      <c r="AM8" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN8" s="13"/>
-      <c r="AO8" s="13"/>
-      <c r="AP8"/>
-      <c r="AQ8" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR8" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS8" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT8" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU8" s="13"/>
-      <c r="AV8" s="14"/>
-      <c r="AW8" s="13"/>
-      <c r="AX8" s="13"/>
-      <c r="AY8" s="13"/>
-      <c r="AZ8" s="13"/>
-      <c r="BA8" s="13"/>
-      <c r="BB8" s="13"/>
-      <c r="BC8" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD8" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE8" s="13"/>
-      <c r="BF8" s="13"/>
-      <c r="BG8" s="13"/>
-      <c r="BH8" s="14"/>
-      <c r="BI8"/>
-      <c r="BJ8" s="23" t="inlineStr">
+      <c r="BJ7" s="23" t="inlineStr">
         <is>
           <t>5.4 kg</t>
         </is>
       </c>
-      <c r="BK8" s="23" t="inlineStr">
+      <c r="BK7" s="23" t="inlineStr">
         <is>
           <t>5.40 kg</t>
         </is>
       </c>
-      <c r="BL8" s="23" t="inlineStr">
+      <c r="BL7" s="23" t="inlineStr">
         <is>
           <t>31.2 x 30.5 x 118 cm</t>
         </is>
       </c>
-      <c r="BM8" s="23" t="inlineStr">
+      <c r="BM7" s="23" t="inlineStr">
         <is>
           <t>31.20 x 30.50 x 118.00 cm</t>
         </is>
       </c>
-      <c r="BN8" s="23" t="inlineStr">
+      <c r="BN7" s="23" t="inlineStr">
         <is>
           <t>7.52 kg</t>
         </is>
       </c>
-      <c r="BO8" s="23" t="inlineStr">
+      <c r="BO7" s="23" t="inlineStr">
         <is>
           <t>7.52 kg</t>
         </is>
       </c>
-      <c r="BP8" s="23" t="inlineStr">
+      <c r="BP7" s="23" t="inlineStr">
         <is>
           <t>75.8 x 33 x 28.8 cm</t>
         </is>
       </c>
-      <c r="BQ8" s="23" t="inlineStr">
+      <c r="BQ7" s="23" t="inlineStr">
         <is>
           <t>75.80 x 33.00 x 28.80 cm</t>
         </is>
       </c>
-      <c r="BR8" s="13" t="inlineStr">
+      <c r="BR7" s="13" t="inlineStr">
         <is>
           <t>轻型标准大件</t>
         </is>
@@ -3073,42 +2851,35 @@
     <hyperlink ref="L4" r:id="rId19" tooltip="https://www.amazon.es/dp/B0FR4TKY99"/>
     <hyperlink ref="M4" r:id="rId20" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N4" r:id="rId21"/>
-    <hyperlink ref="C5" r:id="rId22" tooltip="https://www.amazon.es/dp/B0D2KT41N3"/>
-    <hyperlink ref="G5" r:id="rId23" tooltip="https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0D2KT41N3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J5" r:id="rId24" tooltip="https://www.amazon.es/dp/B0D2KT41N3?psc=1"/>
-    <hyperlink ref="K5" r:id="rId25" tooltip="https://images-na.ssl-images-amazon.com/images/I/71zwr1xxvzL._AC_US600_.jpg"/>
-    <hyperlink ref="L5" r:id="rId26" tooltip="https://www.amazon.es/dp/B0D2KT41N3"/>
+    <hyperlink ref="C5" r:id="rId22" tooltip="https://www.amazon.es/dp/B0H2D3H8RR"/>
+    <hyperlink ref="G5" r:id="rId23" tooltip="https://www.amazon.es/stores/Ultenic/page/0909B0E2-6E16-41A6-9F7F-96DB127DBF91?lp_asin=B0H2D3H8RR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J5" r:id="rId24" tooltip="https://www.amazon.es/dp/B0H2D3H8RR?psc=1"/>
+    <hyperlink ref="K5" r:id="rId25" tooltip="https://m.media-amazon.com/images/I/31WDLyP9wrL._AC_US600_.jpg"/>
+    <hyperlink ref="L5" r:id="rId26" tooltip="https://www.amazon.es/dp/B0H2D3H8RR"/>
     <hyperlink ref="M5" r:id="rId27" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N5" r:id="rId28"/>
-    <hyperlink ref="C6" r:id="rId29" tooltip="https://www.amazon.es/dp/B0H2D3H8RR"/>
-    <hyperlink ref="G6" r:id="rId30" tooltip="https://www.amazon.es/stores/Ultenic/page/0909B0E2-6E16-41A6-9F7F-96DB127DBF91?lp_asin=B0H2D3H8RR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J6" r:id="rId31" tooltip="https://www.amazon.es/dp/B0H2D3H8RR?psc=1"/>
-    <hyperlink ref="K6" r:id="rId32" tooltip="https://m.media-amazon.com/images/I/31WDLyP9wrL._AC_US600_.jpg"/>
-    <hyperlink ref="L6" r:id="rId33" tooltip="https://www.amazon.es/dp/B0H2D3H8RR"/>
+    <hyperlink ref="C6" r:id="rId29" tooltip="https://www.amazon.es/dp/B0H8ZM49W9"/>
+    <hyperlink ref="G6" r:id="rId30" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=KSIWEHDSS"/>
+    <hyperlink ref="J6" r:id="rId31" tooltip="https://www.amazon.es/dp/B0H8ZM49W9?psc=1"/>
+    <hyperlink ref="K6" r:id="rId32" tooltip="https://images-na.ssl-images-amazon.com/images/I/61BFtnogDAL._AC_US600_.jpg"/>
+    <hyperlink ref="L6" r:id="rId33" tooltip="https://www.amazon.es/dp/B0H8ZM49W9"/>
     <hyperlink ref="M6" r:id="rId34" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N6" r:id="rId35"/>
-    <hyperlink ref="C7" r:id="rId36" tooltip="https://www.amazon.es/dp/B0H8ZM49W9"/>
-    <hyperlink ref="G7" r:id="rId37" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=KSIWEHDSS"/>
-    <hyperlink ref="J7" r:id="rId38" tooltip="https://www.amazon.es/dp/B0H8ZM49W9?psc=1"/>
-    <hyperlink ref="K7" r:id="rId39" tooltip="https://images-na.ssl-images-amazon.com/images/I/61BFtnogDAL._AC_US600_.jpg"/>
-    <hyperlink ref="L7" r:id="rId40" tooltip="https://www.amazon.es/dp/B0H8ZM49W9"/>
-    <hyperlink ref="M7" r:id="rId41" tooltip="https://www.amazon.es/b?node=218878925031"/>
-    <hyperlink ref="N7" r:id="rId42"/>
-    <hyperlink ref="AW7" r:id="rId43" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1IIXB8MBW34P6"/>
-    <hyperlink ref="C8" r:id="rId44" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
-    <hyperlink ref="G8" r:id="rId45" tooltip="https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J8" r:id="rId46" tooltip="https://www.amazon.es/dp/B0DGV9F4X3?psc=1"/>
-    <hyperlink ref="K8" r:id="rId47" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ZOUuPZaJL._AC_US600_.jpg"/>
-    <hyperlink ref="L8" r:id="rId48" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
-    <hyperlink ref="M8" r:id="rId49" tooltip="https://www.amazon.es/b?node=218878925031"/>
-    <hyperlink ref="N8" r:id="rId50"/>
+    <hyperlink ref="AW6" r:id="rId36" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1IIXB8MBW34P6"/>
+    <hyperlink ref="C7" r:id="rId37" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
+    <hyperlink ref="G7" r:id="rId38" tooltip="https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J7" r:id="rId39" tooltip="https://www.amazon.es/dp/B0DGV9F4X3?psc=1"/>
+    <hyperlink ref="K7" r:id="rId40" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ZOUuPZaJL._AC_US600_.jpg"/>
+    <hyperlink ref="L7" r:id="rId41" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
+    <hyperlink ref="M7" r:id="rId42" tooltip="https://www.amazon.es/b?node=218878925031"/>
+    <hyperlink ref="N7" r:id="rId43"/>
   </hyperlinks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -3172,7 +2943,7 @@
         <v>339.0</v>
       </c>
       <c r="G2" s="22">
-        <v>0.502283105022831</v>
+        <v>0.7783018867924528</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3193,70 +2964,49 @@
         <v>304.3277777777778</v>
       </c>
       <c r="G3" s="22">
-        <v>0.136986301369863</v>
+        <v>0.21226415094339623</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>Ultenic</t>
         </is>
       </c>
       <c r="B4" s="15">
-        <v>466</v>
+        <v>4</v>
       </c>
       <c r="C4" s="15">
-        <v>18593</v>
+        <v>912</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="20">
-        <v>39.89914163090129</v>
+        <v>228.0</v>
       </c>
       <c r="G4" s="22">
-        <v>0.3546423135464231</v>
+        <v>0.0047169811320754715</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Ultenic</t>
+          <t>KSIWEHDSS</t>
         </is>
       </c>
       <c r="B5" s="15">
         <v>4</v>
       </c>
       <c r="C5" s="15">
-        <v>912</v>
+        <v>144</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="20">
-        <v>228.0</v>
+        <v>36.0</v>
       </c>
       <c r="G5" s="22">
-        <v>0.0030441400304414</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>KSIWEHDSS</t>
-        </is>
-      </c>
-      <c r="B6" s="15">
-        <v>4</v>
-      </c>
-      <c r="C6" s="15">
-        <v>144</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="20">
-        <v>36.0</v>
-      </c>
-      <c r="G6" s="22">
-        <v>0.0030441400304414</v>
+        <v>0.0047169811320754715</v>
       </c>
     </row>
   </sheetData>
@@ -3320,18 +3070,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>1310</v>
+        <v>844</v>
       </c>
       <c r="C2" s="15">
-        <v>298024</v>
+        <v>279431</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>227.4992366412214</v>
+        <v>331.0793838862559</v>
       </c>
       <c r="G2" s="22">
-        <v>0.9969558599695586</v>
+        <v>0.9952830188679245</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3352,7 +3102,7 @@
         <v>36.0</v>
       </c>
       <c r="G3" s="22">
-        <v>0.0030441400304414</v>
+        <v>0.0047169811320754715</v>
       </c>
     </row>
   </sheetData>
